--- a/记录1.xlsx
+++ b/记录1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects_\JiaBi_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A7699A-7D5F-4C27-9596-ED43FB2C7924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FEB21E-85EB-4624-A6FA-3EF824D0929A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="17">
   <si>
     <t>IoU</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,23 +74,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">TransUNet(Enhancer+Distillation+loss) </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Transunet(Enhancer+Distillation)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>N_Transunet(Enhancer+Distillation)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRUE Baseline Transunet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TRUE OURS Transunet</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sens</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -113,13 +116,32 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -131,12 +153,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -149,9 +174,16 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -611,7 +643,7 @@
       <c r="K9" s="2"/>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="2"/>
@@ -699,7 +731,7 @@
       <c r="K14" s="2"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.15">
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="2"/>
@@ -743,26 +775,28 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B17" s="2"/>
       <c r="C17" s="1">
-        <v>0.82169999999999999</v>
+        <v>0.83289999999999997</v>
       </c>
       <c r="D17" s="2">
-        <v>0.69989999999999997</v>
+        <v>0.71650000000000003</v>
       </c>
       <c r="E17" s="2">
-        <v>0.79290000000000005</v>
+        <v>0.84650000000000003</v>
       </c>
       <c r="F17" s="1">
-        <v>0.98680000000000001</v>
+        <v>0.98150000000000004</v>
       </c>
       <c r="G17" s="2">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="H17" s="2"/>
+        <v>0.96830000000000005</v>
+      </c>
+      <c r="H17" s="2">
+        <v>0.82730000000000004</v>
+      </c>
       <c r="I17" s="2">
-        <v>4.28</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2">
@@ -772,7 +806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -784,7 +818,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -795,8 +829,9 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L19" s="2"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
@@ -809,8 +844,10 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B21" s="2"/>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -819,7 +856,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>6</v>
@@ -840,29 +877,30 @@
       <c r="L21" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B22" s="2"/>
       <c r="C22" s="1">
-        <v>0.83030000000000004</v>
+        <v>0.82809999999999995</v>
       </c>
       <c r="D22" s="2">
-        <v>0.71379999999999999</v>
+        <v>0.70979999999999999</v>
       </c>
       <c r="E22" s="2">
-        <v>0.83660000000000001</v>
+        <v>0.85470000000000002</v>
       </c>
       <c r="F22" s="1">
-        <v>0.98240000000000005</v>
+        <v>0.97989999999999999</v>
       </c>
       <c r="G22" s="2">
-        <v>0.96879999999999999</v>
+        <v>0.9677</v>
       </c>
       <c r="H22" s="2">
-        <v>0.83560000000000001</v>
+        <v>0.81100000000000005</v>
       </c>
       <c r="I22" s="2">
-        <v>4.83</v>
+        <v>5.84</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2">
@@ -871,8 +909,9 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -883,9 +922,13 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B24" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B24" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -895,84 +938,88 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="B25" s="2"/>
+      <c r="C25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="K25" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="M25" s="2"/>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B26" s="2"/>
-      <c r="C26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>9</v>
+      <c r="C26" s="2">
+        <v>0.8327</v>
+      </c>
+      <c r="D26" s="2">
+        <v>0.71589999999999998</v>
+      </c>
+      <c r="E26" s="2">
+        <v>0.8488</v>
+      </c>
+      <c r="F26" s="2">
+        <v>0.98150000000000004</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0.96870000000000001</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0.82479999999999998</v>
+      </c>
+      <c r="I26" s="2">
+        <v>4.97</v>
       </c>
       <c r="J26" s="2"/>
-      <c r="K26" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="K26" s="2">
+        <v>50</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="2"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="2"/>
-      <c r="C27" s="1">
-        <v>0.83289999999999997</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0.71650000000000003</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.84650000000000003</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0.98150000000000004</v>
-      </c>
-      <c r="G27" s="2">
-        <v>0.96830000000000005</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0.82730000000000004</v>
-      </c>
-      <c r="I27" s="2">
-        <v>4.1399999999999997</v>
-      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
       <c r="J27" s="2"/>
-      <c r="K27" s="2">
-        <v>50</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -983,20 +1030,10 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1008,7 +1045,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>

--- a/记录1.xlsx
+++ b/记录1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects_\JiaBi_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FEB21E-85EB-4624-A6FA-3EF824D0929A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29990F1A-85D5-4347-B276-DF69C4FB2575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="23">
   <si>
     <t>IoU</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -87,6 +87,30 @@
   </si>
   <si>
     <t>Sens</t>
+  </si>
+  <si>
+    <t>ANFC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNET</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UNET++</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transunet_Ours</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jiabi_Origin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>All_Fil_N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -448,10 +472,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N31"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
+    <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="37.75" customWidth="1"/>
     <col min="3" max="3" width="17.75" customWidth="1"/>
     <col min="4" max="4" width="17.375" customWidth="1"/>
@@ -461,7 +485,12 @@
     <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -478,7 +507,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B3" s="2"/>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -510,7 +539,7 @@
       </c>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B4" s="2"/>
       <c r="C4" s="1">
         <v>0.82369999999999999</v>
@@ -542,7 +571,7 @@
       </c>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -554,7 +583,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
@@ -568,7 +597,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B7" s="2"/>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -599,7 +628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B8" s="2"/>
       <c r="C8" s="1">
         <v>0.82899999999999996</v>
@@ -630,7 +659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -642,7 +671,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B10" s="5" t="s">
         <v>12</v>
       </c>
@@ -656,7 +685,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B11" s="2"/>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -687,7 +716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B12" s="2"/>
       <c r="C12" s="1">
         <v>0.83079999999999998</v>
@@ -718,7 +747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -730,7 +759,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
@@ -744,7 +773,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
       <c r="B16" s="2"/>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -1056,6 +1085,638 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A34" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B37" s="2"/>
+      <c r="C37" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B38" s="2"/>
+      <c r="C38" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="D38" s="2">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="E38" s="2">
+        <v>0.66410000000000002</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0.97460000000000002</v>
+      </c>
+      <c r="G38" s="2">
+        <v>0.94369999999999998</v>
+      </c>
+      <c r="H38" s="2">
+        <v>0.75449999999999995</v>
+      </c>
+      <c r="I38" s="2">
+        <v>28.45</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2">
+        <v>50</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B40" s="1"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B42" s="2"/>
+      <c r="C42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B43" s="2"/>
+      <c r="C43" s="1">
+        <v>0.6895</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0.53969999999999996</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0.69169999999999998</v>
+      </c>
+      <c r="F43" s="1">
+        <v>0.97070000000000001</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0.94169999999999998</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0.72430000000000005</v>
+      </c>
+      <c r="I43" s="2">
+        <v>29.84</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2">
+        <v>50</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B47" s="2"/>
+      <c r="C47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B48" s="2"/>
+      <c r="C48" s="1">
+        <v>0.71189999999999998</v>
+      </c>
+      <c r="D48" s="2">
+        <v>0.56440000000000001</v>
+      </c>
+      <c r="E48" s="2">
+        <v>0.76770000000000005</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.96150000000000002</v>
+      </c>
+      <c r="G48" s="2">
+        <v>0.94099999999999995</v>
+      </c>
+      <c r="H48" s="2">
+        <v>0.68779999999999997</v>
+      </c>
+      <c r="I48" s="2">
+        <v>28.09</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2">
+        <v>50</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B51" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B52" s="2"/>
+      <c r="C52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B53" s="2"/>
+      <c r="C53" s="1">
+        <v>0.71250000000000002</v>
+      </c>
+      <c r="D53" s="2">
+        <v>0.5655</v>
+      </c>
+      <c r="E53" s="2">
+        <v>0.77529999999999999</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0.95930000000000004</v>
+      </c>
+      <c r="G53" s="2">
+        <v>0.94040000000000001</v>
+      </c>
+      <c r="H53" s="2">
+        <v>0.68440000000000001</v>
+      </c>
+      <c r="I53" s="2">
+        <v>26.92</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2">
+        <v>50</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="A56" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B58" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B59" s="2"/>
+      <c r="C59" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B60" s="2"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2">
+        <v>50</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B62" s="1"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="2"/>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B64" s="2"/>
+      <c r="C64" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J64" s="2"/>
+      <c r="K64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B65" s="2"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2">
+        <v>50</v>
+      </c>
+      <c r="L65" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B69" s="2"/>
+      <c r="C69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J69" s="2"/>
+      <c r="K69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B70" s="2"/>
+      <c r="C70" s="1">
+        <v>0.75009999999999999</v>
+      </c>
+      <c r="D70" s="2">
+        <v>0.61129999999999995</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.82310000000000005</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0.9587</v>
+      </c>
+      <c r="G70" s="2">
+        <v>0.94479999999999997</v>
+      </c>
+      <c r="H70" s="2">
+        <v>0.70779999999999998</v>
+      </c>
+      <c r="I70" s="2">
+        <v>20.440000000000001</v>
+      </c>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2">
+        <v>50</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B74" s="2"/>
+      <c r="C74" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J74" s="2"/>
+      <c r="K74" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B75" s="2"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2">
+        <v>50</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/记录1.xlsx
+++ b/记录1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects_\JiaBi_new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29990F1A-85D5-4347-B276-DF69C4FB2575}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943B944D-9077-4EC2-AB0E-0A8BD8541BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="26">
   <si>
     <t>IoU</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -110,6 +110,18 @@
   </si>
   <si>
     <t>All_Fil_N</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transunet_Ours_VT_Turn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transunet_VT_Turn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -1476,13 +1488,27 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B60" s="2"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
+      <c r="C60" s="1">
+        <v>0.73740000000000006</v>
+      </c>
+      <c r="D60" s="2">
+        <v>0.59619999999999995</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0.71889999999999998</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0.97519999999999996</v>
+      </c>
+      <c r="G60" s="2">
+        <v>0.9486</v>
+      </c>
+      <c r="H60" s="2">
+        <v>0.78510000000000002</v>
+      </c>
+      <c r="I60" s="2">
+        <v>19.41</v>
+      </c>
       <c r="J60" s="2"/>
       <c r="K60" s="2">
         <v>50</v>
@@ -1565,13 +1591,27 @@
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B65" s="2"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
+      <c r="C65" s="1">
+        <v>0.74839999999999995</v>
+      </c>
+      <c r="D65" s="2">
+        <v>0.60819999999999996</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.72909999999999997</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0.97709999999999997</v>
+      </c>
+      <c r="G65" s="2">
+        <v>0.9506</v>
+      </c>
+      <c r="H65" s="2">
+        <v>0.78969999999999996</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2">
         <v>50</v>
@@ -1657,7 +1697,7 @@
       </c>
     </row>
     <row r="73" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C73" s="2"/>
@@ -1703,18 +1743,184 @@
     </row>
     <row r="75" spans="2:12" x14ac:dyDescent="0.15">
       <c r="B75" s="2"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
+      <c r="C75" s="1">
+        <v>0.75429999999999997</v>
+      </c>
+      <c r="D75" s="2">
+        <v>0.61580000000000001</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0.79579999999999995</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0.96650000000000003</v>
+      </c>
+      <c r="G75" s="2">
+        <v>0.94850000000000001</v>
+      </c>
+      <c r="H75" s="2">
+        <v>0.73550000000000004</v>
+      </c>
+      <c r="I75" s="2">
+        <v>18.86</v>
+      </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2">
         <v>50</v>
       </c>
       <c r="L75" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B79" s="2"/>
+      <c r="C79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" s="2"/>
+      <c r="K79" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L79" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B80" s="2"/>
+      <c r="C80" s="1">
+        <v>0.78810000000000002</v>
+      </c>
+      <c r="D80" s="2">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0.82620000000000005</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0.97160000000000002</v>
+      </c>
+      <c r="G80" s="2">
+        <v>0.95669999999999999</v>
+      </c>
+      <c r="H80" s="2">
+        <v>0.77280000000000004</v>
+      </c>
+      <c r="I80" s="2">
+        <v>15.52</v>
+      </c>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2">
+        <v>50</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B83" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B84" s="2"/>
+      <c r="C84" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J84" s="2"/>
+      <c r="K84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="B85" s="2"/>
+      <c r="C85" s="1">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="D85" s="2">
+        <v>0.65759999999999996</v>
+      </c>
+      <c r="E85" s="2">
+        <v>0.78990000000000005</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0.97789999999999999</v>
+      </c>
+      <c r="G85" s="2">
+        <v>0.9587</v>
+      </c>
+      <c r="H85" s="2">
+        <v>0.80669999999999997</v>
+      </c>
+      <c r="I85" s="2">
+        <v>14.43</v>
+      </c>
+      <c r="J85" s="2"/>
+      <c r="K85" s="2">
+        <v>50</v>
+      </c>
+      <c r="L85" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/记录1.xlsx
+++ b/记录1.xlsx
@@ -1,135 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects_\JiaBi_new\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943B944D-9077-4EC2-AB0E-0A8BD8541BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="32">
+  <si>
+    <t>Jiabi_Origin</t>
+  </si>
+  <si>
+    <t>UNET_512</t>
+  </si>
+  <si>
+    <t>Dice</t>
+  </si>
   <si>
     <t>IoU</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>Spec</t>
+  </si>
+  <si>
+    <t>Acc</t>
+  </si>
+  <si>
+    <t>Prec</t>
+  </si>
+  <si>
+    <t>HD95</t>
   </si>
   <si>
     <t>Epoch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>LR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1e-4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dice</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Recall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spec</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Acc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Prec</t>
-  </si>
-  <si>
-    <t>HD95</t>
-  </si>
-  <si>
-    <t>UNET_512</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Unet++</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Transunet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>N_Transunet(Enhancer+Distillation)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TRUE Baseline Transunet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sens</t>
   </si>
   <si>
     <t>TRUE OURS Transunet</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Sens</t>
   </si>
   <si>
     <t>ANFC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UNET</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>UNET++</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Transunet_Ours</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Jiabi_Origin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>All_Fil_N</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>--lambda_mse 10.0 --lambda_grad 30.0</t>
+  </si>
+  <si>
+    <t>EarlyStop at 44</t>
+  </si>
+  <si>
+    <t>--lambda_mse 10.0 --lambda_grad 10.0</t>
+  </si>
+  <si>
+    <t>EarlyStop at 45</t>
+  </si>
+  <si>
+    <t>--lambda_mse 20.0 --lambda_grad 20.0</t>
+  </si>
+  <si>
+    <t>Transunet_CV_Only</t>
+  </si>
+  <si>
+    <t>Transunet_VT_Turn</t>
   </si>
   <si>
     <t>Transunet_Ours_VT_Turn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Transunet_VT_Turn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,30 +146,159 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -170,17 +307,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -188,47 +506,344 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -478,14 +1093,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N85"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N100"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
     <col min="2" max="2" width="37.75" customWidth="1"/>
@@ -494,17 +1109,18 @@
     <col min="5" max="5" width="14.625" customWidth="1"/>
     <col min="6" max="6" width="20.375" customWidth="1"/>
     <col min="7" max="7" width="14.125" customWidth="1"/>
-    <col min="8" max="8" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="13" max="13" width="59.8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -519,57 +1135,57 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14">
       <c r="B3" s="2"/>
       <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14">
       <c r="B4" s="2"/>
       <c r="C4" s="1">
-        <v>0.82369999999999999</v>
+        <v>0.8237</v>
       </c>
       <c r="D4" s="2">
-        <v>0.70320000000000005</v>
+        <v>0.7032</v>
       </c>
       <c r="E4" s="2">
-        <v>0.82269999999999999</v>
+        <v>0.8227</v>
       </c>
       <c r="F4" s="1">
-        <v>0.98319999999999996</v>
+        <v>0.9832</v>
       </c>
       <c r="G4" s="2">
         <v>0.9677</v>
       </c>
       <c r="H4" s="2">
-        <v>0.83460000000000001</v>
+        <v>0.8346</v>
       </c>
       <c r="I4" s="2">
         <v>6.12</v>
@@ -578,12 +1194,12 @@
       <c r="K4" s="2">
         <v>50</v>
       </c>
-      <c r="L4" s="3" t="s">
-        <v>3</v>
+      <c r="L4" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14">
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -595,9 +1211,9 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14">
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -609,56 +1225,56 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14">
       <c r="B7" s="2"/>
       <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="B8" s="2"/>
       <c r="C8" s="1">
-        <v>0.82899999999999996</v>
+        <v>0.829</v>
       </c>
       <c r="D8" s="2">
-        <v>0.71089999999999998</v>
+        <v>0.7109</v>
       </c>
       <c r="E8" s="2">
-        <v>0.82489999999999997</v>
+        <v>0.8249</v>
       </c>
       <c r="F8" s="1">
-        <v>0.98419999999999996</v>
+        <v>0.9842</v>
       </c>
       <c r="G8" s="2">
-        <v>0.96870000000000001</v>
+        <v>0.9687</v>
       </c>
       <c r="H8" s="2">
-        <v>0.84319999999999995</v>
+        <v>0.8432</v>
       </c>
       <c r="I8" s="2">
         <v>4.5</v>
@@ -667,11 +1283,11 @@
       <c r="K8" s="2">
         <v>50</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="L8" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -683,9 +1299,9 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B10" s="5" t="s">
-        <v>12</v>
+    <row r="10" spans="1:14">
+      <c r="B10" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -697,69 +1313,69 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14">
       <c r="B11" s="2"/>
       <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="H11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12" s="2"/>
       <c r="C12" s="1">
-        <v>0.83079999999999998</v>
+        <v>0.8308</v>
       </c>
       <c r="D12" s="2">
-        <v>0.71340000000000003</v>
+        <v>0.7134</v>
       </c>
       <c r="E12" s="2">
-        <v>0.83079999999999998</v>
+        <v>0.8308</v>
       </c>
       <c r="F12" s="1">
-        <v>0.98370000000000002</v>
+        <v>0.9837</v>
       </c>
       <c r="G12" s="2">
-        <v>0.96899999999999997</v>
+        <v>0.969</v>
       </c>
       <c r="H12" s="2">
-        <v>0.84009999999999996</v>
+        <v>0.8401</v>
       </c>
       <c r="I12" s="2">
-        <v>5.0599999999999996</v>
+        <v>5.06</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2">
         <v>50</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.15">
+      <c r="L12" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -771,9 +1387,9 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.15">
-      <c r="B15" s="4" t="s">
-        <v>13</v>
+    <row r="15" spans="1:14">
+      <c r="B15" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -785,69 +1401,69 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14">
       <c r="B16" s="2"/>
       <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13">
       <c r="B17" s="2"/>
       <c r="C17" s="1">
-        <v>0.83289999999999997</v>
+        <v>0.8329</v>
       </c>
       <c r="D17" s="2">
-        <v>0.71650000000000003</v>
+        <v>0.7165</v>
       </c>
       <c r="E17" s="2">
-        <v>0.84650000000000003</v>
+        <v>0.8465</v>
       </c>
       <c r="F17" s="1">
-        <v>0.98150000000000004</v>
+        <v>0.9815</v>
       </c>
       <c r="G17" s="2">
-        <v>0.96830000000000005</v>
+        <v>0.9683</v>
       </c>
       <c r="H17" s="2">
-        <v>0.82730000000000004</v>
+        <v>0.8273</v>
       </c>
       <c r="I17" s="2">
-        <v>4.1399999999999997</v>
+        <v>4.14</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2">
         <v>50</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+      <c r="L17" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -859,7 +1475,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -872,9 +1488,9 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -888,57 +1504,57 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="2"/>
       <c r="C21" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M21" s="2"/>
     </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="2"/>
       <c r="C22" s="1">
-        <v>0.82809999999999995</v>
+        <v>0.8281</v>
       </c>
       <c r="D22" s="2">
-        <v>0.70979999999999999</v>
+        <v>0.7098</v>
       </c>
       <c r="E22" s="2">
-        <v>0.85470000000000002</v>
+        <v>0.8547</v>
       </c>
       <c r="F22" s="1">
-        <v>0.97989999999999999</v>
+        <v>0.9799</v>
       </c>
       <c r="G22" s="2">
         <v>0.9677</v>
       </c>
       <c r="H22" s="2">
-        <v>0.81100000000000005</v>
+        <v>0.811</v>
       </c>
       <c r="I22" s="2">
         <v>5.84</v>
@@ -947,12 +1563,12 @@
       <c r="K22" s="2">
         <v>50</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
+      <c r="L22" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="M22" s="2"/>
     </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
@@ -966,9 +1582,9 @@
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
     </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -982,57 +1598,57 @@
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="2"/>
       <c r="C25" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J25" s="2"/>
       <c r="K25" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M25" s="2"/>
     </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:13">
       <c r="B26" s="2"/>
       <c r="C26" s="2">
         <v>0.8327</v>
       </c>
       <c r="D26" s="2">
-        <v>0.71589999999999998</v>
+        <v>0.7159</v>
       </c>
       <c r="E26" s="2">
         <v>0.8488</v>
       </c>
       <c r="F26" s="2">
-        <v>0.98150000000000004</v>
+        <v>0.9815</v>
       </c>
       <c r="G26" s="2">
-        <v>0.96870000000000001</v>
+        <v>0.9687</v>
       </c>
       <c r="H26" s="2">
-        <v>0.82479999999999998</v>
+        <v>0.8248</v>
       </c>
       <c r="I26" s="2">
         <v>4.97</v>
@@ -1041,12 +1657,12 @@
       <c r="K26" s="2">
         <v>50</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
+      <c r="L26" s="9" t="s">
+        <v>11</v>
       </c>
       <c r="M26" s="2"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -1060,7 +1676,7 @@
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
     </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
@@ -1074,7 +1690,7 @@
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
     </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
@@ -1086,7 +1702,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1098,14 +1714,14 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12">
       <c r="A34" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
       <c r="B36" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
@@ -1118,56 +1734,56 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12">
       <c r="B37" s="2"/>
       <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="G37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="I37" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J37" s="2"/>
       <c r="K37" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
       <c r="B38" s="2"/>
       <c r="C38" s="1">
         <v>0.69</v>
       </c>
       <c r="D38" s="2">
-        <v>0.54100000000000004</v>
+        <v>0.541</v>
       </c>
       <c r="E38" s="2">
-        <v>0.66410000000000002</v>
+        <v>0.6641</v>
       </c>
       <c r="F38" s="1">
-        <v>0.97460000000000002</v>
+        <v>0.9746</v>
       </c>
       <c r="G38" s="2">
-        <v>0.94369999999999998</v>
+        <v>0.9437</v>
       </c>
       <c r="H38" s="2">
-        <v>0.75449999999999995</v>
+        <v>0.7545</v>
       </c>
       <c r="I38" s="2">
         <v>28.45</v>
@@ -1176,11 +1792,11 @@
       <c r="K38" s="2">
         <v>50</v>
       </c>
-      <c r="L38" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="L38" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1193,7 +1809,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:12">
       <c r="B40" s="1"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
@@ -1206,9 +1822,9 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:12">
       <c r="B41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
@@ -1221,56 +1837,56 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:12">
       <c r="B42" s="2"/>
       <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E42" s="1" t="s">
+      <c r="F42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="G42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="H42" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="I42" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J42" s="2"/>
       <c r="K42" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
       <c r="B43" s="2"/>
       <c r="C43" s="1">
         <v>0.6895</v>
       </c>
       <c r="D43" s="2">
-        <v>0.53969999999999996</v>
+        <v>0.5397</v>
       </c>
       <c r="E43" s="2">
-        <v>0.69169999999999998</v>
+        <v>0.6917</v>
       </c>
       <c r="F43" s="1">
-        <v>0.97070000000000001</v>
+        <v>0.9707</v>
       </c>
       <c r="G43" s="2">
-        <v>0.94169999999999998</v>
+        <v>0.9417</v>
       </c>
       <c r="H43" s="2">
-        <v>0.72430000000000005</v>
+        <v>0.7243</v>
       </c>
       <c r="I43" s="2">
         <v>29.84</v>
@@ -1279,13 +1895,13 @@
       <c r="K43" s="2">
         <v>50</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="L43" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
       <c r="B46" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
@@ -1297,56 +1913,56 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:12">
       <c r="B47" s="2"/>
       <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E47" s="1" t="s">
+      <c r="F47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="H47" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="I47" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J47" s="2"/>
       <c r="K47" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
       <c r="B48" s="2"/>
       <c r="C48" s="1">
-        <v>0.71189999999999998</v>
+        <v>0.7119</v>
       </c>
       <c r="D48" s="2">
-        <v>0.56440000000000001</v>
+        <v>0.5644</v>
       </c>
       <c r="E48" s="2">
-        <v>0.76770000000000005</v>
+        <v>0.7677</v>
       </c>
       <c r="F48" s="1">
-        <v>0.96150000000000002</v>
+        <v>0.9615</v>
       </c>
       <c r="G48" s="2">
-        <v>0.94099999999999995</v>
+        <v>0.941</v>
       </c>
       <c r="H48" s="2">
-        <v>0.68779999999999997</v>
+        <v>0.6878</v>
       </c>
       <c r="I48" s="2">
         <v>28.09</v>
@@ -1355,13 +1971,13 @@
       <c r="K48" s="2">
         <v>50</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="L48" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="B51" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -1372,57 +1988,58 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" spans="1:12">
       <c r="B52" s="2"/>
       <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E52" s="1" t="s">
+      <c r="F52" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="H52" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="I52" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J52" s="2"/>
       <c r="K52" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="B53" s="2"/>
       <c r="C53" s="1">
-        <v>0.71250000000000002</v>
+        <v>0.7125</v>
       </c>
       <c r="D53" s="2">
         <v>0.5655</v>
       </c>
       <c r="E53" s="2">
-        <v>0.77529999999999999</v>
+        <v>0.7753</v>
       </c>
       <c r="F53" s="1">
-        <v>0.95930000000000004</v>
+        <v>0.9593</v>
       </c>
       <c r="G53" s="2">
-        <v>0.94040000000000001</v>
+        <v>0.9404</v>
       </c>
       <c r="H53" s="2">
-        <v>0.68440000000000001</v>
+        <v>0.6844</v>
       </c>
       <c r="I53" s="2">
         <v>26.92</v>
@@ -1431,18 +2048,68 @@
       <c r="K53" s="2">
         <v>50</v>
       </c>
-      <c r="L53" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="L53" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" spans="1:12">
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" spans="1:12">
       <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" spans="1:12">
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" spans="1:12">
       <c r="B58" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -1455,56 +2122,56 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:12">
       <c r="B59" s="2"/>
       <c r="C59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E59" s="1" t="s">
+      <c r="F59" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="G59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="H59" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="I59" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J59" s="2"/>
       <c r="K59" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12">
       <c r="B60" s="2"/>
       <c r="C60" s="1">
-        <v>0.73740000000000006</v>
+        <v>0.7374</v>
       </c>
       <c r="D60" s="2">
-        <v>0.59619999999999995</v>
+        <v>0.5962</v>
       </c>
       <c r="E60" s="2">
-        <v>0.71889999999999998</v>
+        <v>0.7189</v>
       </c>
       <c r="F60" s="1">
-        <v>0.97519999999999996</v>
+        <v>0.9752</v>
       </c>
       <c r="G60" s="2">
         <v>0.9486</v>
       </c>
       <c r="H60" s="2">
-        <v>0.78510000000000002</v>
+        <v>0.7851</v>
       </c>
       <c r="I60" s="2">
         <v>19.41</v>
@@ -1513,11 +2180,11 @@
       <c r="K60" s="2">
         <v>50</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
+      <c r="L60" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -1530,7 +2197,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:12">
       <c r="B62" s="1"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -1543,9 +2210,9 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:12">
       <c r="B63" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1558,71 +2225,97 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:12">
       <c r="B64" s="2"/>
       <c r="C64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1" t="s">
+      <c r="F64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="G64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="H64" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H64" s="2" t="s">
+      <c r="I64" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J64" s="2"/>
       <c r="K64" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13">
       <c r="B65" s="2"/>
       <c r="C65" s="1">
-        <v>0.74839999999999995</v>
+        <v>0.7484</v>
       </c>
       <c r="D65" s="2">
-        <v>0.60819999999999996</v>
+        <v>0.6082</v>
       </c>
       <c r="E65" s="2">
-        <v>0.72909999999999997</v>
+        <v>0.7291</v>
       </c>
       <c r="F65" s="1">
-        <v>0.97709999999999997</v>
+        <v>0.9771</v>
       </c>
       <c r="G65" s="2">
         <v>0.9506</v>
       </c>
       <c r="H65" s="2">
-        <v>0.78969999999999996</v>
+        <v>0.7897</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J65" s="2"/>
       <c r="K65" s="2">
         <v>50</v>
       </c>
-      <c r="L65" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L65" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2"/>
+    </row>
+    <row r="67" spans="2:13">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+    </row>
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1633,72 +2326,97 @@
       <c r="I68" s="2"/>
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.15">
+      <c r="L68" s="2"/>
+    </row>
+    <row r="69" spans="2:13">
       <c r="B69" s="2"/>
       <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="G69" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="H69" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H69" s="2" t="s">
+      <c r="I69" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J69" s="2"/>
       <c r="K69" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13">
       <c r="B70" s="2"/>
       <c r="C70" s="1">
-        <v>0.75009999999999999</v>
+        <v>0.7501</v>
       </c>
       <c r="D70" s="2">
-        <v>0.61129999999999995</v>
+        <v>0.6113</v>
       </c>
       <c r="E70" s="2">
-        <v>0.82310000000000005</v>
+        <v>0.8231</v>
       </c>
       <c r="F70" s="1">
         <v>0.9587</v>
       </c>
       <c r="G70" s="2">
-        <v>0.94479999999999997</v>
+        <v>0.9448</v>
       </c>
       <c r="H70" s="2">
-        <v>0.70779999999999998</v>
+        <v>0.7078</v>
       </c>
       <c r="I70" s="2">
-        <v>20.440000000000001</v>
+        <v>20.44</v>
       </c>
       <c r="J70" s="2"/>
       <c r="K70" s="2">
         <v>50</v>
       </c>
-      <c r="L70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B73" s="4" t="s">
-        <v>20</v>
+      <c r="L70" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13">
+      <c r="B71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+    </row>
+    <row r="72" spans="2:13">
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2"/>
+    </row>
+    <row r="73" spans="2:13">
+      <c r="B73" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -1709,57 +2427,60 @@
       <c r="I73" s="2"/>
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B74" s="2"/>
+      <c r="L73" s="2"/>
+    </row>
+    <row r="74" spans="2:13">
+      <c r="B74" s="10" t="s">
+        <v>24</v>
+      </c>
       <c r="C74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E74" s="1" t="s">
+      <c r="F74" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="G74" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="H74" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H74" s="2" t="s">
+      <c r="I74" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="J74" s="2"/>
       <c r="K74" s="1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13">
       <c r="B75" s="2"/>
-      <c r="C75" s="1">
-        <v>0.75429999999999997</v>
-      </c>
-      <c r="D75" s="2">
-        <v>0.61580000000000001</v>
+      <c r="C75" s="6">
+        <v>0.7543</v>
+      </c>
+      <c r="D75" s="7">
+        <v>0.6158</v>
       </c>
       <c r="E75" s="2">
-        <v>0.79579999999999995</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0.96650000000000003</v>
-      </c>
-      <c r="G75" s="2">
-        <v>0.94850000000000001</v>
+        <v>0.7958</v>
+      </c>
+      <c r="F75" s="6">
+        <v>0.9665</v>
+      </c>
+      <c r="G75" s="7">
+        <v>0.9485</v>
       </c>
       <c r="H75" s="2">
-        <v>0.73550000000000004</v>
+        <v>0.7355</v>
       </c>
       <c r="I75" s="2">
         <v>18.86</v>
@@ -1768,14 +2489,59 @@
       <c r="K75" s="2">
         <v>50</v>
       </c>
-      <c r="L75" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B78" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="L75" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2">
+        <v>0.7534</v>
+      </c>
+      <c r="D76" s="2">
+        <v>0.6146</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.8075</v>
+      </c>
+      <c r="F76" s="2">
+        <v>0.9632</v>
+      </c>
+      <c r="G76" s="2">
+        <v>0.9473</v>
+      </c>
+      <c r="H76" s="2">
+        <v>0.725</v>
+      </c>
+      <c r="I76" s="2">
+        <v>18.87</v>
+      </c>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2">
+        <v>100</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M76" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="2:13">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+    </row>
+    <row r="78" spans="2:13">
+      <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -1785,73 +2551,109 @@
       <c r="I78" s="2"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B79" s="2"/>
-      <c r="C79" s="1" t="s">
+      <c r="L78" s="2"/>
+    </row>
+    <row r="79" spans="2:13">
+      <c r="B79" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+    </row>
+    <row r="80" spans="2:13">
+      <c r="B80" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E79" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="H80" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H79" s="2" t="s">
+      <c r="I80" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I79" s="2" t="s">
+      <c r="J80" s="2"/>
+      <c r="K80" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J79" s="2"/>
-      <c r="K79" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L79" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B80" s="2"/>
-      <c r="C80" s="1">
-        <v>0.78810000000000002</v>
-      </c>
-      <c r="D80" s="2">
-        <v>0.65800000000000003</v>
-      </c>
-      <c r="E80" s="2">
-        <v>0.82620000000000005</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0.97160000000000002</v>
-      </c>
-      <c r="G80" s="2">
-        <v>0.95669999999999999</v>
-      </c>
-      <c r="H80" s="2">
-        <v>0.77280000000000004</v>
-      </c>
-      <c r="I80" s="2">
-        <v>15.52</v>
-      </c>
-      <c r="J80" s="2"/>
-      <c r="K80" s="2">
+      <c r="L80" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="2:13">
+      <c r="B81" s="2"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2">
         <v>50</v>
       </c>
-      <c r="L80" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="83" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B83" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="L81" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="2:13">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2">
+        <v>0.7504</v>
+      </c>
+      <c r="D82" s="2">
+        <v>0.6109</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0.8274</v>
+      </c>
+      <c r="F82" s="2">
+        <v>0.9581</v>
+      </c>
+      <c r="G82" s="2">
+        <v>0.9444</v>
+      </c>
+      <c r="H82" s="2">
+        <v>0.7041</v>
+      </c>
+      <c r="I82" s="2">
+        <v>19.76</v>
+      </c>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2">
+        <v>100</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="M82" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="2:13">
+      <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
@@ -1861,94 +2663,390 @@
       <c r="I83" s="2"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
-    </row>
-    <row r="84" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B84" s="2"/>
-      <c r="C84" s="1" t="s">
+      <c r="L83" s="2"/>
+    </row>
+    <row r="84" spans="2:13">
+      <c r="B84" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+    </row>
+    <row r="85" spans="2:13">
+      <c r="B85" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E84" s="1" t="s">
+      <c r="F85" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="G85" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="H85" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H84" s="2" t="s">
+      <c r="I85" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I84" s="2" t="s">
+      <c r="J85" s="2"/>
+      <c r="K85" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J84" s="2"/>
-      <c r="K84" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="L84" s="1" t="s">
+      <c r="L85" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="2:13">
+      <c r="B86" s="2"/>
+      <c r="C86" s="1">
+        <v>0.7537</v>
+      </c>
+      <c r="D86" s="2">
+        <v>0.6143</v>
+      </c>
+      <c r="E86" s="2">
+        <v>0.7906</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0.9664</v>
+      </c>
+      <c r="G86" s="2">
+        <v>0.9481</v>
+      </c>
+      <c r="H86" s="2">
+        <v>0.7377</v>
+      </c>
+      <c r="I86" s="2">
+        <v>19</v>
+      </c>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2">
+        <v>50</v>
+      </c>
+      <c r="L86" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="2:13">
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2"/>
+      <c r="K87" s="2"/>
+      <c r="L87" s="3"/>
+    </row>
+    <row r="89" spans="2:13">
+      <c r="B89" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+    </row>
+    <row r="90" spans="2:13">
+      <c r="B90" s="2"/>
+      <c r="C90" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B85" s="2"/>
-      <c r="C85" s="1">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="D85" s="2">
-        <v>0.65759999999999996</v>
-      </c>
-      <c r="E85" s="2">
-        <v>0.78990000000000005</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0.97789999999999999</v>
-      </c>
-      <c r="G85" s="2">
+      <c r="D90" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J90" s="2"/>
+      <c r="K90" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L90" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="2:13">
+      <c r="B91" s="2"/>
+      <c r="C91" s="2">
+        <v>0.7531</v>
+      </c>
+      <c r="D91" s="2">
+        <v>0.6139</v>
+      </c>
+      <c r="E91" s="2">
+        <v>0.7828</v>
+      </c>
+      <c r="F91" s="2">
+        <v>0.9662</v>
+      </c>
+      <c r="G91" s="2">
+        <v>0.9483</v>
+      </c>
+      <c r="H91" s="7">
+        <v>0.7444</v>
+      </c>
+      <c r="I91" s="7">
+        <v>18.43</v>
+      </c>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2">
+        <v>50</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="2:13">
+      <c r="B92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2"/>
+      <c r="L92" s="3"/>
+    </row>
+    <row r="93" spans="2:13">
+      <c r="B93" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="2"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
+    </row>
+    <row r="94" spans="2:13">
+      <c r="B94" s="2"/>
+      <c r="C94" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" s="2"/>
+      <c r="K94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L94" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="2:13">
+      <c r="B95" s="2"/>
+      <c r="C95" s="1">
+        <v>0.7881</v>
+      </c>
+      <c r="D95" s="2">
+        <v>0.658</v>
+      </c>
+      <c r="E95" s="2">
+        <v>0.8262</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0.9716</v>
+      </c>
+      <c r="G95" s="2">
+        <v>0.9567</v>
+      </c>
+      <c r="H95" s="2">
+        <v>0.7728</v>
+      </c>
+      <c r="I95" s="2">
+        <v>15.52</v>
+      </c>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2">
+        <v>50</v>
+      </c>
+      <c r="L95" s="9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="2:13">
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+    </row>
+    <row r="97" spans="2:12">
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="2"/>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+    </row>
+    <row r="98" spans="2:12">
+      <c r="B98" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2"/>
+    </row>
+    <row r="99" spans="2:12">
+      <c r="B99" s="2"/>
+      <c r="C99" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J99" s="2"/>
+      <c r="K99" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12">
+      <c r="B100" s="2"/>
+      <c r="C100" s="1">
+        <v>0.788</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0.6576</v>
+      </c>
+      <c r="E100" s="2">
+        <v>0.7899</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0.9779</v>
+      </c>
+      <c r="G100" s="2">
         <v>0.9587</v>
       </c>
-      <c r="H85" s="2">
-        <v>0.80669999999999997</v>
-      </c>
-      <c r="I85" s="2">
+      <c r="H100" s="2">
+        <v>0.8067</v>
+      </c>
+      <c r="I100" s="2">
         <v>14.43</v>
       </c>
-      <c r="J85" s="2"/>
-      <c r="K85" s="2">
+      <c r="J100" s="2"/>
+      <c r="K100" s="2">
         <v>50</v>
       </c>
-      <c r="L85" s="3" t="s">
-        <v>3</v>
+      <c r="L100" s="9" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/记录1.xlsx
+++ b/记录1.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="41">
   <si>
     <t>Jiabi_Origin</t>
   </si>
@@ -121,10 +121,37 @@
     <t>Transunet_CV_Only</t>
   </si>
   <si>
+    <t>_5_7</t>
+  </si>
+  <si>
+    <t>Transunet_Ours_CLAHE_Only</t>
+  </si>
+  <si>
+    <t>Transunet_Ours_Green_Only</t>
+  </si>
+  <si>
+    <t>Transunet_Ours_Sigmoid</t>
+  </si>
+  <si>
     <t>Transunet_VT_Turn</t>
   </si>
   <si>
     <t>Transunet_Ours_VT_Turn</t>
+  </si>
+  <si>
+    <t>4_24_Best</t>
+  </si>
+  <si>
+    <t>Transunet_Green_CV_Only</t>
+  </si>
+  <si>
+    <t>5_15</t>
+  </si>
+  <si>
+    <t>5_8_Best</t>
+  </si>
+  <si>
+    <t>Transunet_Ours_Green_Only_Sigmoid</t>
   </si>
 </sst>
 </file>
@@ -319,6 +346,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -422,12 +455,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -630,7 +657,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -654,16 +681,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -675,51 +702,51 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -754,7 +781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -773,19 +800,34 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="22" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1099,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N183"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.625" customWidth="1"/>
@@ -1110,6 +1152,7 @@
     <col min="6" max="6" width="20.375" customWidth="1"/>
     <col min="7" max="7" width="14.125" customWidth="1"/>
     <col min="8" max="8" width="9.5" customWidth="1"/>
+    <col min="11" max="11" width="20.5083333333333" customWidth="1"/>
     <col min="13" max="13" width="59.8" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1194,7 +1237,7 @@
       <c r="K4" s="2">
         <v>50</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="13" t="s">
         <v>11</v>
       </c>
       <c r="N4" s="2"/>
@@ -1283,7 +1326,7 @@
       <c r="K8" s="2">
         <v>50</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1371,7 +1414,7 @@
       <c r="K12" s="2">
         <v>50</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1459,7 +1502,7 @@
       <c r="K17" s="2">
         <v>50</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1563,7 +1606,7 @@
       <c r="K22" s="2">
         <v>50</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="13" t="s">
         <v>11</v>
       </c>
       <c r="M22" s="2"/>
@@ -1657,7 +1700,7 @@
       <c r="K26" s="2">
         <v>50</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="13" t="s">
         <v>11</v>
       </c>
       <c r="M26" s="2"/>
@@ -1792,7 +1835,7 @@
       <c r="K38" s="2">
         <v>50</v>
       </c>
-      <c r="L38" s="9" t="s">
+      <c r="L38" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1895,7 +1938,7 @@
       <c r="K43" s="2">
         <v>50</v>
       </c>
-      <c r="L43" s="9" t="s">
+      <c r="L43" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1971,7 +2014,7 @@
       <c r="K48" s="2">
         <v>50</v>
       </c>
-      <c r="L48" s="9" t="s">
+      <c r="L48" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2048,7 +2091,7 @@
       <c r="K53" s="2">
         <v>50</v>
       </c>
-      <c r="L53" s="9" t="s">
+      <c r="L53" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2180,7 +2223,7 @@
       <c r="K60" s="2">
         <v>50</v>
       </c>
-      <c r="L60" s="9" t="s">
+      <c r="L60" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2267,13 +2310,13 @@
       <c r="E65" s="2">
         <v>0.7291</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65" s="6">
         <v>0.9771</v>
       </c>
-      <c r="G65" s="2">
+      <c r="G65" s="7">
         <v>0.9506</v>
       </c>
-      <c r="H65" s="2">
+      <c r="H65" s="7">
         <v>0.7897</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -2283,7 +2326,7 @@
       <c r="K65" s="2">
         <v>50</v>
       </c>
-      <c r="L65" s="9" t="s">
+      <c r="L65" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2386,7 +2429,7 @@
       <c r="K70" s="2">
         <v>50</v>
       </c>
-      <c r="L70" s="9" t="s">
+      <c r="L70" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2430,7 +2473,7 @@
       <c r="L73" s="2"/>
     </row>
     <row r="74" spans="2:13">
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="14" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="1" t="s">
@@ -2464,63 +2507,63 @@
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="2"/>
-      <c r="C75" s="6">
+      <c r="C75" s="8">
         <v>0.7543</v>
       </c>
-      <c r="D75" s="7">
+      <c r="D75" s="8">
         <v>0.6158</v>
       </c>
-      <c r="E75" s="2">
+      <c r="E75" s="1">
         <v>0.7958</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75" s="1">
         <v>0.9665</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G75" s="1">
         <v>0.9485</v>
       </c>
-      <c r="H75" s="2">
+      <c r="H75" s="1">
         <v>0.7355</v>
       </c>
-      <c r="I75" s="2">
+      <c r="I75" s="1">
         <v>18.86</v>
       </c>
       <c r="J75" s="2"/>
       <c r="K75" s="2">
         <v>50</v>
       </c>
-      <c r="L75" s="9" t="s">
+      <c r="L75" s="13" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="2"/>
-      <c r="C76" s="2">
+      <c r="C76" s="1">
         <v>0.7534</v>
       </c>
-      <c r="D76" s="2">
+      <c r="D76" s="1">
         <v>0.6146</v>
       </c>
-      <c r="E76" s="2">
+      <c r="E76" s="1">
         <v>0.8075</v>
       </c>
-      <c r="F76" s="2">
+      <c r="F76" s="1">
         <v>0.9632</v>
       </c>
-      <c r="G76" s="2">
+      <c r="G76" s="1">
         <v>0.9473</v>
       </c>
-      <c r="H76" s="2">
+      <c r="H76" s="1">
         <v>0.725</v>
       </c>
-      <c r="I76" s="2">
+      <c r="I76" s="1">
         <v>18.87</v>
       </c>
       <c r="J76" s="2"/>
       <c r="K76" s="2">
         <v>100</v>
       </c>
-      <c r="L76" s="9" t="s">
+      <c r="L76" s="13" t="s">
         <v>11</v>
       </c>
       <c r="M76" t="s">
@@ -2529,47 +2572,47 @@
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
     <row r="79" spans="2:13">
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
     <row r="80" spans="2:13">
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -2587,10 +2630,10 @@
       <c r="G80" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="2" t="s">
+      <c r="H80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I80" s="2" t="s">
+      <c r="I80" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J80" s="2"/>
@@ -2601,87 +2644,87 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="2:13">
+    <row r="81" spans="1:13">
       <c r="B81" s="2"/>
       <c r="C81" s="1"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
       <c r="J81" s="2"/>
       <c r="K81" s="2">
         <v>50</v>
       </c>
-      <c r="L81" s="9" t="s">
+      <c r="L81" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:13">
+    <row r="82" spans="1:13">
       <c r="B82" s="2"/>
-      <c r="C82" s="2">
+      <c r="C82" s="1">
         <v>0.7504</v>
       </c>
-      <c r="D82" s="2">
+      <c r="D82" s="1">
         <v>0.6109</v>
       </c>
-      <c r="E82" s="7">
+      <c r="E82" s="6">
         <v>0.8274</v>
       </c>
-      <c r="F82" s="2">
+      <c r="F82" s="1">
         <v>0.9581</v>
       </c>
-      <c r="G82" s="2">
+      <c r="G82" s="1">
         <v>0.9444</v>
       </c>
-      <c r="H82" s="2">
+      <c r="H82" s="1">
         <v>0.7041</v>
       </c>
-      <c r="I82" s="2">
+      <c r="I82" s="1">
         <v>19.76</v>
       </c>
       <c r="J82" s="2"/>
       <c r="K82" s="2">
         <v>100</v>
       </c>
-      <c r="L82" s="9" t="s">
+      <c r="L82" s="13" t="s">
         <v>11</v>
       </c>
       <c r="M82" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="2:13">
+    <row r="83" spans="1:13">
       <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="2:13">
-      <c r="B84" s="8" t="s">
+    <row r="84" spans="1:13">
+      <c r="B84" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="2:13">
-      <c r="B85" s="10" t="s">
+    <row r="85" spans="1:13">
+      <c r="B85" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -2699,10 +2742,10 @@
       <c r="G85" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H85" s="2" t="s">
+      <c r="H85" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I85" s="2" t="s">
+      <c r="I85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J85" s="2"/>
@@ -2713,66 +2756,75 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="2:13">
+    <row r="86" spans="1:13">
       <c r="B86" s="2"/>
       <c r="C86" s="1">
         <v>0.7537</v>
       </c>
-      <c r="D86" s="2">
+      <c r="D86" s="1">
         <v>0.6143</v>
       </c>
-      <c r="E86" s="2">
+      <c r="E86" s="1">
         <v>0.7906</v>
       </c>
       <c r="F86" s="1">
         <v>0.9664</v>
       </c>
-      <c r="G86" s="2">
+      <c r="G86" s="1">
         <v>0.9481</v>
       </c>
-      <c r="H86" s="2">
+      <c r="H86" s="1">
         <v>0.7377</v>
       </c>
-      <c r="I86" s="2">
+      <c r="I86" s="1">
         <v>19</v>
       </c>
       <c r="J86" s="2"/>
       <c r="K86" s="2">
         <v>50</v>
       </c>
-      <c r="L86" s="9" t="s">
+      <c r="L86" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="2:13">
+    <row r="87" spans="1:13">
       <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="3"/>
     </row>
-    <row r="89" spans="2:13">
-      <c r="B89" s="8" t="s">
+    <row r="88" spans="1:13">
+      <c r="C88" s="10"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="10"/>
+      <c r="H88" s="10"/>
+      <c r="I88" s="10"/>
+    </row>
+    <row r="89" spans="1:13">
+      <c r="B89" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
+      <c r="E89" s="1"/>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" spans="2:13">
+    <row r="90" spans="1:13">
       <c r="B90" s="2"/>
       <c r="C90" s="1" t="s">
         <v>2</v>
@@ -2789,10 +2841,10 @@
       <c r="G90" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H90" s="2" t="s">
+      <c r="H90" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I90" s="2" t="s">
+      <c r="I90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J90" s="2"/>
@@ -2803,163 +2855,176 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="2:13">
+    <row r="91" spans="1:13">
       <c r="B91" s="2"/>
-      <c r="C91" s="2">
+      <c r="C91" s="1">
         <v>0.7531</v>
       </c>
-      <c r="D91" s="2">
+      <c r="D91" s="1">
         <v>0.6139</v>
       </c>
-      <c r="E91" s="2">
+      <c r="E91" s="1">
         <v>0.7828</v>
       </c>
-      <c r="F91" s="2">
+      <c r="F91" s="1">
         <v>0.9662</v>
       </c>
-      <c r="G91" s="2">
+      <c r="G91" s="1">
         <v>0.9483</v>
       </c>
-      <c r="H91" s="7">
+      <c r="H91" s="1">
         <v>0.7444</v>
       </c>
-      <c r="I91" s="7">
+      <c r="I91" s="1">
         <v>18.43</v>
       </c>
       <c r="J91" s="2"/>
       <c r="K91" s="2">
         <v>50</v>
       </c>
-      <c r="L91" s="9" t="s">
+      <c r="L91" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:13">
+    <row r="92" spans="1:13">
       <c r="B92" s="2"/>
+      <c r="C92" s="10"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="10"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="10"/>
       <c r="J92" s="2"/>
       <c r="K92" s="2"/>
       <c r="L92" s="3"/>
     </row>
-    <row r="93" spans="2:13">
-      <c r="B93" s="4" t="s">
+    <row r="93" spans="1:13">
+      <c r="C93" s="10"/>
+      <c r="D93" s="10"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+    </row>
+    <row r="94" spans="1:13">
+      <c r="A94" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
-    </row>
-    <row r="94" spans="2:13">
       <c r="B94" s="2"/>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2"/>
+    </row>
+    <row r="95" spans="1:13">
+      <c r="A95" s="2"/>
+      <c r="B95" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D95" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E94" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G95" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H94" s="2" t="s">
+      <c r="H95" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I94" s="2" t="s">
+      <c r="I95" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J94" s="2"/>
-      <c r="K94" s="1" t="s">
+      <c r="J95" s="2"/>
+      <c r="K95" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L94" s="1" t="s">
+      <c r="L95" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="2:13">
-      <c r="B95" s="2"/>
-      <c r="C95" s="1">
-        <v>0.7881</v>
-      </c>
-      <c r="D95" s="2">
-        <v>0.658</v>
-      </c>
-      <c r="E95" s="2">
-        <v>0.8262</v>
-      </c>
-      <c r="F95" s="1">
-        <v>0.9716</v>
-      </c>
-      <c r="G95" s="2">
-        <v>0.9567</v>
-      </c>
-      <c r="H95" s="2">
-        <v>0.7728</v>
-      </c>
-      <c r="I95" s="2">
-        <v>15.52</v>
-      </c>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2">
+    <row r="96" spans="1:13">
+      <c r="A96" s="2"/>
+      <c r="B96" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="1">
+        <v>0.7552</v>
+      </c>
+      <c r="D96" s="1">
+        <v>0.6165</v>
+      </c>
+      <c r="E96" s="1">
+        <v>0.8063</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0.9637</v>
+      </c>
+      <c r="G96" s="1">
+        <v>0.9474</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0.7297</v>
+      </c>
+      <c r="I96" s="1">
+        <v>18.89</v>
+      </c>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2">
         <v>50</v>
       </c>
-      <c r="L95" s="9" t="s">
+      <c r="L96" s="13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="2:13">
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
-    </row>
-    <row r="97" spans="2:12">
+    <row r="97" spans="1:12">
+      <c r="A97" s="2"/>
       <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
+      <c r="C97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="2:12">
-      <c r="B98" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
+    <row r="98" spans="1:12">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="2:12">
-      <c r="B99" s="2"/>
+    <row r="99" spans="1:12">
+      <c r="A99" s="2"/>
+      <c r="B99" s="9" t="s">
+        <v>32</v>
+      </c>
       <c r="C99" s="1" t="s">
         <v>2</v>
       </c>
@@ -2989,36 +3054,1082 @@
         <v>10</v>
       </c>
     </row>
-    <row r="100" spans="2:12">
-      <c r="B100" s="2"/>
-      <c r="C100" s="1">
-        <v>0.788</v>
-      </c>
-      <c r="D100" s="2">
-        <v>0.6576</v>
+    <row r="100" spans="1:12">
+      <c r="A100" s="2"/>
+      <c r="B100" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" s="7">
+        <v>0.7567</v>
+      </c>
+      <c r="D100" s="7">
+        <v>0.6184</v>
       </c>
       <c r="E100" s="2">
-        <v>0.7899</v>
-      </c>
-      <c r="F100" s="1">
-        <v>0.9779</v>
+        <v>0.8156</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0.9622</v>
       </c>
       <c r="G100" s="2">
-        <v>0.9587</v>
+        <v>0.9473</v>
       </c>
       <c r="H100" s="2">
-        <v>0.8067</v>
-      </c>
-      <c r="I100" s="2">
-        <v>14.43</v>
+        <v>0.723</v>
+      </c>
+      <c r="I100" s="7">
+        <v>18.05</v>
       </c>
       <c r="J100" s="2"/>
       <c r="K100" s="2">
         <v>50</v>
       </c>
-      <c r="L100" s="9" t="s">
+      <c r="L100" s="13" t="s">
         <v>11</v>
       </c>
+    </row>
+    <row r="101" spans="1:12">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="2"/>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+    </row>
+    <row r="102" spans="1:12">
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="2"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2"/>
+      <c r="L102" s="2"/>
+    </row>
+    <row r="103" spans="1:12">
+      <c r="A103" s="2"/>
+      <c r="B103" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J103" s="2"/>
+      <c r="K103" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12">
+      <c r="B104" s="2"/>
+      <c r="C104" s="2">
+        <v>0.7514</v>
+      </c>
+      <c r="D104" s="2">
+        <v>0.6128</v>
+      </c>
+      <c r="E104" s="2">
+        <v>0.7871</v>
+      </c>
+      <c r="F104" s="2">
+        <v>0.9666</v>
+      </c>
+      <c r="G104" s="2">
+        <v>0.9481</v>
+      </c>
+      <c r="H104" s="2">
+        <v>0.7394</v>
+      </c>
+      <c r="I104" s="2">
+        <v>18.96</v>
+      </c>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2">
+        <v>50</v>
+      </c>
+      <c r="L104" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12">
+      <c r="B105" s="2"/>
+      <c r="C105" s="2">
+        <v>0.7529</v>
+      </c>
+      <c r="D105" s="2">
+        <v>0.6143</v>
+      </c>
+      <c r="E105" s="2">
+        <v>0.7699</v>
+      </c>
+      <c r="F105" s="2"/>
+      <c r="G105" s="2"/>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2"/>
+    </row>
+    <row r="133" spans="2:12">
+      <c r="B133" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+    </row>
+    <row r="134" spans="2:12">
+      <c r="B134" s="2"/>
+      <c r="C134" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J134" s="2"/>
+      <c r="K134" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="2:12">
+      <c r="B135" s="2"/>
+      <c r="C135" s="1">
+        <v>0.7881</v>
+      </c>
+      <c r="D135" s="2">
+        <v>0.658</v>
+      </c>
+      <c r="E135" s="2">
+        <v>0.8262</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0.9716</v>
+      </c>
+      <c r="G135" s="2">
+        <v>0.9567</v>
+      </c>
+      <c r="H135" s="2">
+        <v>0.7728</v>
+      </c>
+      <c r="I135" s="2">
+        <v>15.52</v>
+      </c>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2">
+        <v>50</v>
+      </c>
+      <c r="L135" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" spans="2:12">
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+    </row>
+    <row r="137" spans="2:12">
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+    </row>
+    <row r="138" spans="2:12">
+      <c r="B138" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2"/>
+      <c r="F138" s="2"/>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+    </row>
+    <row r="139" spans="2:12">
+      <c r="B139" s="2"/>
+      <c r="C139" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J139" s="2"/>
+      <c r="K139" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="2:12">
+      <c r="B140" s="2"/>
+      <c r="C140" s="1">
+        <v>0.788</v>
+      </c>
+      <c r="D140" s="2">
+        <v>0.6576</v>
+      </c>
+      <c r="E140" s="2">
+        <v>0.7899</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0.9779</v>
+      </c>
+      <c r="G140" s="2">
+        <v>0.9587</v>
+      </c>
+      <c r="H140" s="2">
+        <v>0.8067</v>
+      </c>
+      <c r="I140" s="2">
+        <v>14.43</v>
+      </c>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2">
+        <v>50</v>
+      </c>
+      <c r="L140" s="13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="2:12">
+      <c r="B146" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2"/>
+      <c r="F146" s="2"/>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
+    </row>
+    <row r="147" spans="2:12">
+      <c r="B147" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F147" s="2"/>
+      <c r="G147" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H147" s="2"/>
+      <c r="I147" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
+    </row>
+    <row r="148" spans="2:12">
+      <c r="B148" s="2"/>
+      <c r="C148" s="11">
+        <v>0.7543</v>
+      </c>
+      <c r="D148" s="11">
+        <v>0.6158</v>
+      </c>
+      <c r="E148" s="11">
+        <v>0.7958</v>
+      </c>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11">
+        <v>18.86</v>
+      </c>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11">
+        <v>50</v>
+      </c>
+      <c r="J148" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="K148" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="L148" s="2"/>
+    </row>
+    <row r="149" spans="2:12">
+      <c r="B149" s="2"/>
+      <c r="C149" s="2">
+        <v>0.7534</v>
+      </c>
+      <c r="D149" s="2">
+        <v>0.6146</v>
+      </c>
+      <c r="E149" s="2">
+        <v>0.8075</v>
+      </c>
+      <c r="F149" s="2"/>
+      <c r="G149" s="2">
+        <v>18.87</v>
+      </c>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2">
+        <v>100</v>
+      </c>
+      <c r="J149" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L149" s="2"/>
+    </row>
+    <row r="150" spans="2:12">
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="2"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
+      <c r="I150" s="2"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+    </row>
+    <row r="151" spans="2:12">
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="2"/>
+      <c r="F151" s="2"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
+      <c r="I151" s="2"/>
+      <c r="J151" s="2"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
+    </row>
+    <row r="152" spans="2:12">
+      <c r="B152" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="2"/>
+      <c r="F152" s="2"/>
+      <c r="G152" s="2"/>
+      <c r="H152" s="2"/>
+      <c r="I152" s="2"/>
+      <c r="J152" s="2"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
+    </row>
+    <row r="153" spans="2:12">
+      <c r="B153" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F153" s="2"/>
+      <c r="G153" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H153" s="2"/>
+      <c r="I153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K153" s="2"/>
+      <c r="L153" s="2"/>
+    </row>
+    <row r="154" spans="2:12">
+      <c r="B154" s="2"/>
+      <c r="C154" s="1"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="2"/>
+      <c r="F154" s="2"/>
+      <c r="G154" s="2"/>
+      <c r="H154" s="2"/>
+      <c r="I154" s="2">
+        <v>50</v>
+      </c>
+      <c r="J154" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
+    </row>
+    <row r="155" spans="2:12">
+      <c r="B155" s="2"/>
+      <c r="C155" s="2">
+        <v>0.7504</v>
+      </c>
+      <c r="D155" s="2">
+        <v>0.6109</v>
+      </c>
+      <c r="E155" s="1">
+        <v>0.8274</v>
+      </c>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2">
+        <v>19.76</v>
+      </c>
+      <c r="H155" s="2"/>
+      <c r="I155" s="2">
+        <v>100</v>
+      </c>
+      <c r="J155" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L155" s="2"/>
+    </row>
+    <row r="156" spans="2:12">
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="E156" s="2"/>
+      <c r="F156" s="2"/>
+      <c r="G156" s="2"/>
+      <c r="H156" s="2"/>
+      <c r="I156" s="2"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+    </row>
+    <row r="157" spans="2:12">
+      <c r="B157" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="2"/>
+      <c r="F157" s="2"/>
+      <c r="G157" s="2"/>
+      <c r="H157" s="2"/>
+      <c r="I157" s="2"/>
+      <c r="J157" s="2"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
+    </row>
+    <row r="158" spans="2:12">
+      <c r="B158" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F158" s="2"/>
+      <c r="G158" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H158" s="2"/>
+      <c r="I158" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J158" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K158" s="2"/>
+      <c r="L158" s="2"/>
+    </row>
+    <row r="159" spans="2:12">
+      <c r="B159" s="2"/>
+      <c r="C159" s="1">
+        <v>0.7537</v>
+      </c>
+      <c r="D159" s="2">
+        <v>0.6143</v>
+      </c>
+      <c r="E159" s="2">
+        <v>0.7906</v>
+      </c>
+      <c r="F159" s="2"/>
+      <c r="G159" s="2">
+        <v>19</v>
+      </c>
+      <c r="H159" s="2"/>
+      <c r="I159" s="2">
+        <v>50</v>
+      </c>
+      <c r="J159" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K159" s="2"/>
+      <c r="L159" s="2"/>
+    </row>
+    <row r="160" spans="2:12">
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="8"/>
+      <c r="F160" s="2"/>
+      <c r="G160" s="2"/>
+      <c r="H160" s="2"/>
+      <c r="I160" s="2"/>
+      <c r="J160" s="3"/>
+      <c r="K160" s="2"/>
+      <c r="L160" s="2"/>
+    </row>
+    <row r="161" spans="1:12">
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="2"/>
+      <c r="F161" s="2"/>
+      <c r="G161" s="2"/>
+      <c r="H161" s="2"/>
+      <c r="I161" s="2"/>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="B162" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="2"/>
+      <c r="F162" s="2"/>
+      <c r="G162" s="2"/>
+      <c r="H162" s="2"/>
+      <c r="I162" s="2"/>
+      <c r="J162" s="2"/>
+      <c r="K162" s="2"/>
+      <c r="L162" s="2"/>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="B163" s="2"/>
+      <c r="C163" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H163" s="2"/>
+      <c r="I163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+    </row>
+    <row r="164" spans="1:12">
+      <c r="B164" s="2"/>
+      <c r="C164" s="2">
+        <v>0.7531</v>
+      </c>
+      <c r="D164" s="2">
+        <v>0.6139</v>
+      </c>
+      <c r="E164" s="2">
+        <v>0.7828</v>
+      </c>
+      <c r="F164" s="2"/>
+      <c r="G164" s="1">
+        <v>18.43</v>
+      </c>
+      <c r="H164" s="2"/>
+      <c r="I164" s="2">
+        <v>50</v>
+      </c>
+      <c r="J164" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
+    </row>
+    <row r="165" spans="1:12">
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="2"/>
+      <c r="F165" s="2"/>
+      <c r="G165" s="2"/>
+      <c r="H165" s="2"/>
+      <c r="I165" s="2"/>
+      <c r="J165" s="3"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
+    </row>
+    <row r="166" spans="1:12">
+      <c r="B166" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="2"/>
+      <c r="F166" s="2"/>
+      <c r="G166" s="2"/>
+      <c r="H166" s="2"/>
+      <c r="I166" s="2"/>
+      <c r="J166" s="2"/>
+      <c r="K166" s="2"/>
+      <c r="L166" s="2"/>
+    </row>
+    <row r="167" spans="1:12">
+      <c r="B167" s="2"/>
+      <c r="C167" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F167" s="2"/>
+      <c r="G167" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H167" s="2"/>
+      <c r="I167" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J167" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L167" s="2"/>
+    </row>
+    <row r="168" spans="1:12">
+      <c r="B168" s="2"/>
+      <c r="C168" s="2">
+        <v>0.7496</v>
+      </c>
+      <c r="D168" s="2">
+        <v>0.6109</v>
+      </c>
+      <c r="E168" s="2">
+        <v>0.8005</v>
+      </c>
+      <c r="F168" s="2"/>
+      <c r="G168" s="1">
+        <v>20.06</v>
+      </c>
+      <c r="H168" s="2"/>
+      <c r="I168" s="2">
+        <v>50</v>
+      </c>
+      <c r="J168" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K168" t="s">
+        <v>38</v>
+      </c>
+      <c r="L168" s="2"/>
+    </row>
+    <row r="169" spans="1:12">
+      <c r="L169" s="2"/>
+    </row>
+    <row r="170" spans="1:12">
+      <c r="A170" t="s">
+        <v>30</v>
+      </c>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="2"/>
+      <c r="F170" s="2"/>
+      <c r="G170" s="2"/>
+      <c r="H170" s="2"/>
+      <c r="I170" s="2"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
+    </row>
+    <row r="171" spans="1:12">
+      <c r="B171" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F171" s="2"/>
+      <c r="G171" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H171" s="2"/>
+      <c r="I171" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J171" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
+    </row>
+    <row r="172" spans="1:12">
+      <c r="B172" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172" s="2">
+        <v>0.7552</v>
+      </c>
+      <c r="D172" s="2">
+        <v>0.6165</v>
+      </c>
+      <c r="E172" s="2">
+        <v>0.8063</v>
+      </c>
+      <c r="F172" s="2"/>
+      <c r="G172" s="2">
+        <v>18.89</v>
+      </c>
+      <c r="H172" s="2"/>
+      <c r="I172" s="2">
+        <v>50</v>
+      </c>
+      <c r="J172" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K172" s="2"/>
+      <c r="L172" s="2"/>
+    </row>
+    <row r="173" spans="1:12">
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="2"/>
+      <c r="I173" s="2"/>
+      <c r="J173" s="2"/>
+      <c r="K173" s="2"/>
+      <c r="L173" s="2"/>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="B175" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F175" s="2"/>
+      <c r="G175" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H175" s="2"/>
+      <c r="I175" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J175" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K175" s="2"/>
+      <c r="L175" s="2"/>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="B176" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C176" s="7">
+        <v>0.7567</v>
+      </c>
+      <c r="D176" s="7">
+        <v>0.6184</v>
+      </c>
+      <c r="E176" s="7">
+        <v>0.8156</v>
+      </c>
+      <c r="F176" s="2"/>
+      <c r="G176" s="7">
+        <v>18.05</v>
+      </c>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2">
+        <v>50</v>
+      </c>
+      <c r="J176" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K176" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L176" s="2"/>
+    </row>
+    <row r="177" spans="2:11">
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="2"/>
+      <c r="H177" s="2"/>
+      <c r="I177" s="2"/>
+      <c r="J177" s="2"/>
+      <c r="K177" s="2"/>
+    </row>
+    <row r="178" spans="2:11">
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="2"/>
+      <c r="F178" s="2"/>
+      <c r="G178" s="2"/>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2"/>
+    </row>
+    <row r="179" spans="2:11">
+      <c r="B179" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F179" s="2"/>
+      <c r="G179" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H179" s="2"/>
+      <c r="I179" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J179" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K179" s="2"/>
+    </row>
+    <row r="180" spans="2:11">
+      <c r="B180" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C180" s="2">
+        <v>0.7514</v>
+      </c>
+      <c r="D180" s="2">
+        <v>0.6128</v>
+      </c>
+      <c r="E180" s="2">
+        <v>0.7871</v>
+      </c>
+      <c r="F180" s="2"/>
+      <c r="G180" s="2">
+        <v>18.96</v>
+      </c>
+      <c r="H180" s="2"/>
+      <c r="I180" s="2">
+        <v>50</v>
+      </c>
+      <c r="J180" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K180" s="2"/>
+    </row>
+    <row r="181" spans="2:11">
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="2"/>
+      <c r="F181" s="2"/>
+      <c r="G181" s="2"/>
+      <c r="H181" s="2"/>
+      <c r="I181" s="2"/>
+      <c r="J181" s="2"/>
+      <c r="K181" s="2"/>
+    </row>
+    <row r="182" spans="2:11">
+      <c r="B182" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F182" s="2"/>
+      <c r="G182" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H182" s="2"/>
+      <c r="I182" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J182" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K182" s="2"/>
+    </row>
+    <row r="183" spans="2:11">
+      <c r="B183" s="2"/>
+      <c r="C183" s="2">
+        <v>0.7529</v>
+      </c>
+      <c r="D183" s="2">
+        <v>0.6143</v>
+      </c>
+      <c r="E183" s="2">
+        <v>0.7699</v>
+      </c>
+      <c r="F183" s="2"/>
+      <c r="G183" s="2">
+        <v>18.48</v>
+      </c>
+      <c r="H183" s="2"/>
+      <c r="I183" s="2">
+        <v>50</v>
+      </c>
+      <c r="J183" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="K183" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
